--- a/apigw/docs/VA_ForWebHookCreation.xlsx
+++ b/apigw/docs/VA_ForWebHookCreation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\cde\apigw\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D35C2AA-858B-4633-B6C6-4F91376A42EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41083BDF-A702-4156-AAEE-8BA8D17A77F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7C94A986-260E-404D-A8F3-3D62DA88CC55}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>#</t>
   </si>
@@ -90,13 +90,34 @@
   </si>
   <si>
     <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_%20ICC_1</t>
+  </si>
+  <si>
+    <t>curl -i -X GET http:/10.65.51.252:8088/va/sov-38alt-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+  </si>
+  <si>
+    <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-crowding -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L4 ICC 1 VA CROWDING</t>
+  </si>
+  <si>
+    <t>SOV 38ALT L4 LIFT LOBBY VA LOITERING</t>
+  </si>
+  <si>
+    <t>Incident Type</t>
+  </si>
+  <si>
+    <t>Curl Command</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +141,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -129,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -152,12 +190,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF303031"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF303031"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF303031"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -166,6 +217,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -501,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD592C5-17A3-4409-8112-0309F849EF9C}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -510,10 +568,13 @@
     <col min="4" max="4" width="29.140625" customWidth="1"/>
     <col min="5" max="5" width="72.5703125" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="34.140625" customWidth="1"/>
+    <col min="11" max="11" width="32.140625" customWidth="1"/>
+    <col min="12" max="12" width="87.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -541,8 +602,17 @@
       <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -570,8 +640,17 @@
       <c r="I2" s="4">
         <v>3</v>
       </c>
+      <c r="J2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -599,6 +678,18 @@
       <c r="I3" s="4">
         <v>3</v>
       </c>
+      <c r="J3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N7" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/apigw/docs/VA_ForWebHookCreation.xlsx
+++ b/apigw/docs/VA_ForWebHookCreation.xlsx
@@ -1,173 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\cde\apigw\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41083BDF-A702-4156-AAEE-8BA8D17A77F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7C94A986-260E-404D-A8F3-3D62DA88CC55}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asset ID </t>
-  </si>
-  <si>
-    <t>Camera URL</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Building </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floor </t>
-  </si>
-  <si>
-    <t>Room/Zone</t>
-  </si>
-  <si>
-    <t>SOV_38ALT_L4_Lift_Lobby</t>
-  </si>
-  <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Lift_Lobby</t>
-  </si>
-  <si>
-    <t>Camera Name</t>
-  </si>
-  <si>
-    <t>SOV 38ALT L4 Lift Lobby</t>
-  </si>
-  <si>
-    <t>VA Name</t>
-  </si>
-  <si>
-    <t>LOITERING</t>
-  </si>
-  <si>
-    <t>CROWDING</t>
-  </si>
-  <si>
-    <t>SOV 38ALT L4 ICC 1</t>
-  </si>
-  <si>
-    <t>SOV_38ALT_L4_ ICC_1</t>
-  </si>
-  <si>
-    <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_%20ICC_1</t>
-  </si>
-  <si>
-    <t>curl -i -X GET http:/10.65.51.252:8088/va/sov-38alt-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
-  </si>
-  <si>
-    <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-crowding -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
-  </si>
-  <si>
-    <t>Sensor</t>
-  </si>
-  <si>
-    <t>SOV 38ALT L4 ICC 1 VA CROWDING</t>
-  </si>
-  <si>
-    <t>SOV 38ALT L4 LIFT LOBBY VA LOITERING</t>
-  </si>
-  <si>
-    <t>Incident Type</t>
-  </si>
-  <si>
-    <t>Curl Command</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <color theme="5"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -190,55 +89,102 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF303031"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF303031"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF303031"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -558,143 +504,1202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCD592C5-17A3-4409-8112-0309F849EF9C}">
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="21.65" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" customWidth="1"/>
-    <col min="4" max="4" width="29.140625" customWidth="1"/>
-    <col min="5" max="5" width="72.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="34.140625" customWidth="1"/>
-    <col min="11" max="11" width="32.140625" customWidth="1"/>
-    <col min="12" max="12" width="87.7109375" customWidth="1"/>
+    <col width="7.54296875" customWidth="1" min="1" max="1"/>
+    <col width="20.54296875" customWidth="1" min="2" max="2"/>
+    <col width="35.453125" customWidth="1" min="3" max="3"/>
+    <col width="33.6328125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="80.36328125" customWidth="1" min="5" max="5"/>
+    <col width="14.81640625" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="34.1796875" customWidth="1" min="10" max="10"/>
+    <col width="32.1796875" customWidth="1" min="11" max="11"/>
+    <col width="121.08984375" bestFit="1" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" ht="21.65" customFormat="1" customHeight="1" s="2">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>VA Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Camera Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asset ID </t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Camera URL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Site</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building </t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Floor </t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Room/Zone</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sensor</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Incident Type</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Curl Command</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21.65" customHeight="1">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 Lift Lobby</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L4_Lift_Lobby</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Lift_Lobby</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 LIFT LOBBY VA LOITERING</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21.65" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>CROWDING</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 ICC 1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L4_ ICC_1</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_%20ICC_1</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 ICC 1 VA CROWDING</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>CROWDING</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-icc-1-crowding -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.65" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SMOKING</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Gate</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Main_Gate</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Gate</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Gate VA SMOKING</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>SMOKING</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-main-gate-smoking -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21.65" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>FIRE</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Gate</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Main_Gate</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Gate</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Gate VA FIRE</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>FIRE</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-main-gate-fire -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.65" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ILLEGAL PARKING</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Carpark Lot 1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Carpark_Lot_1</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Carpark_Lot_1</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Carpark Lot 1 VA ILLEGAL PARKING</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>ILLEGAL PARKING</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-carpark-lot-1-illegal-parking -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="21.65" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L1 Lift Lobby</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L1_Lift Lobby</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L1_Lift Lobby</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L1 Lift Lobby LOITERING</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l1-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.65" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 Corridor o/s War Room</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L4_Corridor_o/s_War_Room</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Corridor_o/s_War_Room</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 Corridor o/s War Room LOITERING</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-corridor-o-s-war-room-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.65" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 Interlock</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L4_Interlock</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L4_Interlock</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L4 Interlock LOITERING</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l4-interlock-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21.65" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L5 Corridor</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L5_Corridor</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L5_Corridor</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L5 Corridor LOITERING</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l5-corridor-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.65" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>INTRUSION</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Side Fencing Fencing</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Side_Fencing</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Side_Fencing</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Side Fencing INTRUSION</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>INTRUSION</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-side-fencing-intrusion -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.65" customHeight="1">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>SMOKING</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Side Fencing Fencing</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Side_Fencing</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Side_Fencing</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Side Fencing SMOKING</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>SMOKING</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-side-fencing-smoking -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21.65" customHeight="1">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>FIRE</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Side Fencing Fencing</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Side_Fencing</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Side_Fencing</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Side Fencing FIRE</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>FIRE</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-side-fencing-fire -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21.65" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Roof Top</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Roof_Top</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Roof_Top</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Roof Top LOITERING</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-roof-top-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21.65" customHeight="1">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L2 Lift Lobby</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L2_Lift Lobby</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Lift Lobby</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L2 Lift Lobby LOITERING</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21.65" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L3 Lift Lobby</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L3_Lift_Lobby</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L3_Lift_Lobby</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="I16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L3_Lift_Lobby LOITERING</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l3-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21.65" customHeight="1">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L2 Main Lobby</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L2_Main_Lobby</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Main_Lobby</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L2 Main Lobby LOITERING</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-main-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21.65" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L2 Reception</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L2_Reception</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L2_Reception</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L2_Reception LOITERING</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l2-reception-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21.65" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Road</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Main_Road</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Road</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Road LOITERING</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-main-road-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21.65" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L6 Lift Lift Lobby</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L6_Lift Lobby</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L6_Lift Lobby</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L6 Lift Lobby LOITERING</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l6-lift-lobby-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21.65" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L5 o/s Cyber Room</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_L5_o/s_Cyber_Room</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_L5_o/s_Cyber_Room</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4">
-        <v>4</v>
-      </c>
-      <c r="I2" s="4">
-        <v>3</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="I21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT L5 o/s Cyber Room LOITERING</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>LOITERING</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-l5-o-s-cyber-room-loitering -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21.65" customHeight="1">
+      <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4">
-        <v>4</v>
-      </c>
-      <c r="I3" s="4">
-        <v>3</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N7" s="6"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>INTRUSION</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Gate Perimiter</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>SOV_38ALT_Main_Gate_Perimeter</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>https://sov38alt-cam.isems-privagate.com/stream.html?src=SOV_38ALT_Main_Gate_Perimeter</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>SOV 38ALT Main Gate Perimiter VA INTRUSION</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>INTRUSION</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>curl -i -X GET http://10.65.51.252:8088/va/sov-38alt-main-gate-perimeter-intrusion -u "vizzio@imops.local:xAJHkkm7m3V5MhtF0xGM"</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{DCE694EB-1AF6-4B87-835C-A8EBF182B677}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{AD3AFD6F-87EE-4900-A71F-2EF6DDB75440}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
